--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46202</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 29274-2026</t>
+          <t>A 28631-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46202</v>
+        <v>46198</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -900,26 +900,21 @@
           <t>NORSJÖ</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>10.2</v>
+        <v>19.6</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -930,21 +925,150 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>16</v>
       </c>
       <c r="T4" t="n">
+        <v>68</v>
+      </c>
+      <c r="U4" t="n">
+        <v>68</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Smalfotad taggsvamp
+Spökfransskivling
+Torrmusseron
+Blanksvart spiklav
+Blå taggsvamp
+Kolflarnlav
+Lunglav
+Tallfingersvamp
+Tallriska
+Talltagel
+Talltita
+Tretåig hackspett
+Bårdlav
+Plattlummer
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 28631-2026 artfynd.xlsx", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 28631-2026 karta.png", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 28631-2026 georefererad karta.tif", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 28631-2026 FSC-klagomål.docx", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 28631-2026 FSC-klagomål mail.docx", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 28631-2026 tillsynsbegäran.docx", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 28631-2026 tillsynsbegäran mail.docx", "A 28631-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 28631-2026 prioriterade fågelarter.docx", "A 28631-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 29274-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NORSJÖ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="n">
         <v>73</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>73</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -964,120 +1088,120 @@
 Ormbär</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 29274-2026 artfynd.xlsx", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 29274-2026 karta.png", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 29274-2026 georefererad karta.tif", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/knärot/A 29274-2026 karta knärot.png", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 29274-2026 FSC-klagomål.docx", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 29274-2026 FSC-klagomål mail.docx", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 29274-2026 tillsynsbegäran.docx", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 29274-2026 tillsynsbegäran mail.docx", "A 29274-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 29274-2026 prioriterade fågelarter.docx", "A 29274-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 34223-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>46253</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NORSJÖ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NORSJÖ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>8.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>9</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>3</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>15</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>27</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1096,120 +1220,120 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 34223-2026 artfynd.xlsx", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 34223-2026 karta.png", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 34223-2026 georefererad karta.tif", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/knärot/A 34223-2026 karta knärot.png", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 34223-2026 FSC-klagomål.docx", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 34223-2026 FSC-klagomål mail.docx", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 34223-2026 tillsynsbegäran.docx", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 34223-2026 tillsynsbegäran mail.docx", "A 34223-2026")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 34223-2026 prioriterade fågelarter.docx", "A 34223-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 29121-2024</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45482</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NORSJÖ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NORSJÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>7</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>13</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>34</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>34</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1226,116 +1350,116 @@
 Ögonpyrola</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 29121-2024 artfynd.xlsx", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 29121-2024 karta.png", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 29121-2024 georefererad karta.tif", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/knärot/A 29121-2024 karta knärot.png", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 29121-2024 FSC-klagomål.docx", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 29121-2024 FSC-klagomål mail.docx", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 29121-2024 tillsynsbegäran.docx", "A 29121-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 29121-2024 tillsynsbegäran mail.docx", "A 29121-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 36927-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NORSJÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORSJÖ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>12</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>50</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>50</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Doftskinn
@@ -1351,116 +1475,116 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 36927-2026 artfynd.xlsx", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 36927-2026 karta.png", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 36927-2026 georefererad karta.tif", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 36927-2026 FSC-klagomål.docx", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 36927-2026 FSC-klagomål mail.docx", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 36927-2026 tillsynsbegäran.docx", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 36927-2026 tillsynsbegäran mail.docx", "A 36927-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 36927-2026 prioriterade fågelarter.docx", "A 36927-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 40423-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45895</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORSJÖ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORSJÖ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>20.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>11</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>69</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>69</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1475,115 +1599,115 @@
 Kärrfibbla</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 40423-2025 artfynd.xlsx", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 40423-2025 karta.png", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 40423-2025 georefererad karta.tif", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/knärot/A 40423-2025 karta knärot.png", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 40423-2025 FSC-klagomål.docx", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 40423-2025 FSC-klagomål mail.docx", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 40423-2025 tillsynsbegäran.docx", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 40423-2025 tillsynsbegäran mail.docx", "A 40423-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 40423-2025 prioriterade fågelarter.docx", "A 40423-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 40718-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45897</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORSJÖ</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORSJÖ</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.3</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>10</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>12</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gammelgransskål
@@ -1597,157 +1721,39 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 40718-2025 artfynd.xlsx", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 40718-2025 karta.png", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 40718-2025 georefererad karta.tif", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 40718-2025 FSC-klagomål.docx", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 40718-2025 FSC-klagomål mail.docx", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 40718-2025 tillsynsbegäran.docx", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 40718-2025 tillsynsbegäran mail.docx", "A 40718-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 40718-2025 prioriterade fågelarter.docx", "A 40718-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 28631-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORSJÖ</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="n">
-        <v>59</v>
-      </c>
-      <c r="U10" t="n">
-        <v>59</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Blanksvart spiklav
-Kolflarnlav
-Lunglav
-Talltagel
-Talltita
-Tretåig hackspett
-Bårdlav
-Plattlummer
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/artfynd/A 28631-2026 artfynd.xlsx", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor/A 28631-2026 karta.png", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/kartor_geotiff/A 28631-2026 georefererad karta.tif", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomål/A 28631-2026 FSC-klagomål.docx", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/klagomålsmail/A 28631-2026 FSC-klagomål mail.docx", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsyn/A 28631-2026 tillsynsbegäran.docx", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/tillsynsmail/A 28631-2026 tillsynsbegäran mail.docx", "A 28631-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2417/fåglar/A 28631-2026 prioriterade fågelarter.docx", "A 28631-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1768,7 +1774,7 @@
         <v>45853</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1893,7 +1899,7 @@
         <v>46220</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2023,7 @@
         <v>45616</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2131,7 +2137,7 @@
         <v>45600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2250,7 +2256,7 @@
         <v>45922</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2364,7 +2370,7 @@
         <v>45174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2473,7 +2479,7 @@
         <v>46214</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2587,7 +2593,7 @@
         <v>46260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2711,7 @@
         <v>44545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2818,7 +2824,7 @@
         <v>45531</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2930,7 +2936,7 @@
         <v>46211</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3047,7 +3053,7 @@
         <v>46211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3164,7 +3170,7 @@
         <v>46227</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3281,7 +3287,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3393,7 +3399,7 @@
         <v>45981</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3511,7 @@
         <v>44853</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3612,7 +3618,7 @@
         <v>45587</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3730,7 @@
         <v>45520</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3839,7 +3845,7 @@
         <v>45918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3950,7 +3956,7 @@
         <v>45544</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4061,7 +4067,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4182,7 @@
         <v>46220</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4287,7 +4293,7 @@
         <v>46281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4402,7 +4408,7 @@
         <v>46283</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4513,7 +4519,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4624,7 +4630,7 @@
         <v>45701</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4739,7 +4745,7 @@
         <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4844,7 +4850,7 @@
         <v>45639</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4954,7 +4960,7 @@
         <v>45889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5064,7 +5070,7 @@
         <v>45889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5174,7 +5180,7 @@
         <v>44462</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5284,7 +5290,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5393,7 +5399,7 @@
         <v>46010</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5503,7 +5509,7 @@
         <v>45432</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5617,7 +5623,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5727,7 +5733,7 @@
         <v>46190</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5836,7 +5842,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5946,7 +5952,7 @@
         <v>46133</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6056,7 +6062,7 @@
         <v>45621</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6166,7 +6172,7 @@
         <v>46272</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6276,7 +6282,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6386,7 +6392,7 @@
         <v>46135</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6496,7 +6502,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6569,7 +6575,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6642,7 +6648,7 @@
         <v>44462</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6720,7 +6726,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6798,7 +6804,7 @@
         <v>44466</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6871,7 +6877,7 @@
         <v>44742</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6944,7 +6950,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7017,7 +7023,7 @@
         <v>44869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7095,7 +7101,7 @@
         <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7168,7 +7174,7 @@
         <v>44476</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7246,7 +7252,7 @@
         <v>44820</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7319,7 +7325,7 @@
         <v>44872</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7392,7 +7398,7 @@
         <v>44879</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7465,7 +7471,7 @@
         <v>44487</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7538,7 +7544,7 @@
         <v>44470</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7611,7 +7617,7 @@
         <v>44869</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7689,7 +7695,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7762,7 +7768,7 @@
         <v>44872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7840,7 +7846,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7918,7 +7924,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7996,7 +8002,7 @@
         <v>45173</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8080,7 @@
         <v>44608</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8153,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8226,7 @@
         <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8299,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8371,7 +8377,7 @@
         <v>45478</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8444,7 +8450,7 @@
         <v>45016</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8517,7 +8523,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8590,7 +8596,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8668,7 +8674,7 @@
         <v>45085</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8741,7 +8747,7 @@
         <v>45085</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8814,7 +8820,7 @@
         <v>45644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8892,7 +8898,7 @@
         <v>45580</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8970,7 +8976,7 @@
         <v>45184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9043,7 +9049,7 @@
         <v>44893</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9116,7 +9122,7 @@
         <v>45209</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9189,7 +9195,7 @@
         <v>44999</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9262,7 +9268,7 @@
         <v>44594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9335,7 +9341,7 @@
         <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9408,7 +9414,7 @@
         <v>45183</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9481,7 +9487,7 @@
         <v>45147</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9554,7 +9560,7 @@
         <v>45161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9627,7 +9633,7 @@
         <v>45517</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9705,7 +9711,7 @@
         <v>45604</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9783,7 +9789,7 @@
         <v>45587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9861,7 +9867,7 @@
         <v>44893</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9934,7 +9940,7 @@
         <v>45208</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10007,7 +10013,7 @@
         <v>45174</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10080,7 +10086,7 @@
         <v>45107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10158,7 +10164,7 @@
         <v>45461</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10231,7 +10237,7 @@
         <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10304,7 +10310,7 @@
         <v>45049</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10377,7 +10383,7 @@
         <v>45170</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10450,7 +10456,7 @@
         <v>45561</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10523,7 +10529,7 @@
         <v>45172</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10596,7 +10602,7 @@
         <v>45511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10669,7 +10675,7 @@
         <v>45511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10742,7 +10748,7 @@
         <v>45594</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10820,7 +10826,7 @@
         <v>45754</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10893,7 +10899,7 @@
         <v>45524</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10971,7 +10977,7 @@
         <v>45240</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11049,7 +11055,7 @@
         <v>46136</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11127,7 +11133,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11205,7 +11211,7 @@
         <v>45163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11278,7 +11284,7 @@
         <v>45824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11351,7 +11357,7 @@
         <v>45890</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11429,7 +11435,7 @@
         <v>45891</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11507,7 +11513,7 @@
         <v>45895</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11585,7 +11591,7 @@
         <v>45104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11663,7 +11669,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11736,7 +11742,7 @@
         <v>45896</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11809,7 +11815,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11882,7 +11888,7 @@
         <v>45901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11960,7 +11966,7 @@
         <v>45898</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12038,7 +12044,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12116,7 +12122,7 @@
         <v>45623</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12189,7 +12195,7 @@
         <v>45310</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12262,7 +12268,7 @@
         <v>45511</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12335,7 +12341,7 @@
         <v>45902</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12408,7 +12414,7 @@
         <v>45905</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12486,7 +12492,7 @@
         <v>45846</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12559,7 +12565,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12632,7 +12638,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12710,7 +12716,7 @@
         <v>45877</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12788,7 +12794,7 @@
         <v>44848</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12861,7 +12867,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12939,7 +12945,7 @@
         <v>45912</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13017,7 +13023,7 @@
         <v>45665</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13095,7 +13101,7 @@
         <v>45916</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13173,7 +13179,7 @@
         <v>45168</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13251,7 +13257,7 @@
         <v>45182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13324,7 +13330,7 @@
         <v>45922</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13402,7 +13408,7 @@
         <v>45923</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13475,7 +13481,7 @@
         <v>45923</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13548,7 +13554,7 @@
         <v>45924</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13621,7 +13627,7 @@
         <v>45925</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13699,7 +13705,7 @@
         <v>45694</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13777,7 +13783,7 @@
         <v>45926</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13855,7 +13861,7 @@
         <v>44461</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13928,7 +13934,7 @@
         <v>46143</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14006,7 +14012,7 @@
         <v>46142</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14079,7 +14085,7 @@
         <v>45930</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14157,7 +14163,7 @@
         <v>46142</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14230,7 +14236,7 @@
         <v>45930</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14308,7 +14314,7 @@
         <v>45540</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14386,7 +14392,7 @@
         <v>45244</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14459,7 +14465,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14532,7 +14538,7 @@
         <v>45936</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14610,7 +14616,7 @@
         <v>45943</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14683,7 +14689,7 @@
         <v>45541</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14767,7 @@
         <v>46148</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14834,7 +14840,7 @@
         <v>45168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14912,7 +14918,7 @@
         <v>45628</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14985,7 +14991,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15058,7 +15064,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15131,7 +15137,7 @@
         <v>45947</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15204,7 +15210,7 @@
         <v>45947</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15277,7 +15283,7 @@
         <v>45611</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15350,7 +15356,7 @@
         <v>45947</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15428,7 +15434,7 @@
         <v>45950</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15506,7 +15512,7 @@
         <v>45951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15579,7 +15585,7 @@
         <v>45954</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15657,7 +15663,7 @@
         <v>45957</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15730,7 +15736,7 @@
         <v>46150</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15803,7 +15809,7 @@
         <v>46153</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15881,7 +15887,7 @@
         <v>46153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15959,7 +15965,7 @@
         <v>45156</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16032,7 +16038,7 @@
         <v>45960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16105,7 +16111,7 @@
         <v>45960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16183,7 +16189,7 @@
         <v>45965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16256,7 +16262,7 @@
         <v>45965</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16329,7 +16335,7 @@
         <v>45966</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16402,7 +16408,7 @@
         <v>45971</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16480,7 +16486,7 @@
         <v>45167</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16558,7 +16564,7 @@
         <v>45169</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16631,7 +16637,7 @@
         <v>44945</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16704,7 +16710,7 @@
         <v>45971</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16777,7 +16783,7 @@
         <v>45175</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16850,7 +16856,7 @@
         <v>45973</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16928,7 +16934,7 @@
         <v>45973</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17006,7 +17012,7 @@
         <v>44657</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17084,7 +17090,7 @@
         <v>45609</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17157,7 +17163,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17230,7 +17236,7 @@
         <v>45604</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17308,7 +17314,7 @@
         <v>45530</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17381,7 +17387,7 @@
         <v>45980</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17454,7 +17460,7 @@
         <v>45981</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17527,7 +17533,7 @@
         <v>45157</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17600,7 +17606,7 @@
         <v>45727</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17673,7 +17679,7 @@
         <v>45981</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17746,7 +17752,7 @@
         <v>45981</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17819,7 +17825,7 @@
         <v>46155</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17897,7 +17903,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17970,7 +17976,7 @@
         <v>45163</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18043,7 +18049,7 @@
         <v>45987</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18116,7 +18122,7 @@
         <v>45986</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18194,7 +18200,7 @@
         <v>45485</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18267,7 +18273,7 @@
         <v>45160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18340,7 +18346,7 @@
         <v>45989</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18418,7 +18424,7 @@
         <v>44944</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18491,7 +18497,7 @@
         <v>45988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18564,7 +18570,7 @@
         <v>45157</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18637,7 +18643,7 @@
         <v>45989</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18710,7 +18716,7 @@
         <v>45407</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18788,7 +18794,7 @@
         <v>45993</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18861,7 +18867,7 @@
         <v>45545</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18939,7 +18945,7 @@
         <v>45993</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19012,7 +19018,7 @@
         <v>44867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19090,7 +19096,7 @@
         <v>45257</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19163,7 +19169,7 @@
         <v>45602</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19236,7 +19242,7 @@
         <v>45941</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19309,7 +19315,7 @@
         <v>45161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19382,7 +19388,7 @@
         <v>46160</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19460,7 +19466,7 @@
         <v>46162</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19538,7 +19544,7 @@
         <v>44876</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19616,7 +19622,7 @@
         <v>45551</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19694,7 +19700,7 @@
         <v>45618</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19767,7 +19773,7 @@
         <v>45551</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19845,7 +19851,7 @@
         <v>45551</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19923,7 +19929,7 @@
         <v>45993</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19996,7 +20002,7 @@
         <v>44524</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20069,7 +20075,7 @@
         <v>44510</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20147,7 +20153,7 @@
         <v>46162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20225,7 +20231,7 @@
         <v>44853</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20303,7 +20309,7 @@
         <v>45999</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20376,7 +20382,7 @@
         <v>45548</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20454,7 +20460,7 @@
         <v>44963</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20527,7 +20533,7 @@
         <v>45037</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20600,7 +20606,7 @@
         <v>45947</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20673,7 +20679,7 @@
         <v>46008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20746,7 +20752,7 @@
         <v>46008</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20819,7 +20825,7 @@
         <v>45540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20897,7 +20903,7 @@
         <v>45184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20970,7 +20976,7 @@
         <v>45551</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21043,7 +21049,7 @@
         <v>46020</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21116,7 +21122,7 @@
         <v>45163</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21189,7 +21195,7 @@
         <v>46170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21262,7 +21268,7 @@
         <v>46029</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21335,7 +21341,7 @@
         <v>45750</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21408,7 +21414,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21481,7 +21487,7 @@
         <v>46035</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21554,7 +21560,7 @@
         <v>46035</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21627,7 +21633,7 @@
         <v>46171</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21705,7 +21711,7 @@
         <v>46035</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21778,7 +21784,7 @@
         <v>46035</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21851,7 +21857,7 @@
         <v>46035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21924,7 +21930,7 @@
         <v>45274</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22002,7 +22008,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22075,7 +22081,7 @@
         <v>45511</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22148,7 +22154,7 @@
         <v>45891</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22221,7 +22227,7 @@
         <v>46042</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22294,7 +22300,7 @@
         <v>44556</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22367,7 +22373,7 @@
         <v>46171</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22445,7 +22451,7 @@
         <v>46176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22523,7 +22529,7 @@
         <v>46176</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22596,7 +22602,7 @@
         <v>45533</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22674,7 +22680,7 @@
         <v>46176</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22747,7 +22753,7 @@
         <v>45947</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22820,7 +22826,7 @@
         <v>44468</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22898,7 +22904,7 @@
         <v>46177</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22976,7 +22982,7 @@
         <v>46055</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23049,7 +23055,7 @@
         <v>45947</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23122,7 +23128,7 @@
         <v>45525</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23200,7 +23206,7 @@
         <v>45547</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23273,7 +23279,7 @@
         <v>45085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23346,7 +23352,7 @@
         <v>46062</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23419,7 +23425,7 @@
         <v>45586</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23497,7 +23503,7 @@
         <v>45161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23570,7 +23576,7 @@
         <v>46181</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23648,7 +23654,7 @@
         <v>46183</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23721,7 +23727,7 @@
         <v>46181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23799,7 +23805,7 @@
         <v>46182</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23877,7 +23883,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23955,7 +23961,7 @@
         <v>46183</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24033,7 +24039,7 @@
         <v>45178</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24106,7 +24112,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24184,7 +24190,7 @@
         <v>46183</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24262,7 +24268,7 @@
         <v>46183</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24340,7 +24346,7 @@
         <v>45019</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24418,7 +24424,7 @@
         <v>46083</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24491,7 +24497,7 @@
         <v>46183</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24569,7 +24575,7 @@
         <v>45450</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24642,7 +24648,7 @@
         <v>45462</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24715,7 +24721,7 @@
         <v>45462</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24788,7 +24794,7 @@
         <v>46090</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24861,7 +24867,7 @@
         <v>46090</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24934,7 +24940,7 @@
         <v>45719</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25007,7 +25013,7 @@
         <v>46185</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25085,7 +25091,7 @@
         <v>46185</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25163,7 +25169,7 @@
         <v>45163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25241,7 +25247,7 @@
         <v>45114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25314,7 +25320,7 @@
         <v>45306</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25392,7 +25398,7 @@
         <v>46093</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25465,7 +25471,7 @@
         <v>46189</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25543,7 +25549,7 @@
         <v>46196</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25616,7 +25622,7 @@
         <v>46196</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25694,7 +25700,7 @@
         <v>46196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25767,7 +25773,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25840,7 +25846,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25913,7 +25919,7 @@
         <v>46197</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25991,7 +25997,7 @@
         <v>46106</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26064,7 +26070,7 @@
         <v>46105</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26137,7 +26143,7 @@
         <v>46105</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26210,7 +26216,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26283,7 +26289,7 @@
         <v>45428</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26356,7 +26362,7 @@
         <v>46107</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26429,7 +26435,7 @@
         <v>46107</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26502,7 +26508,7 @@
         <v>45044</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26575,7 +26581,7 @@
         <v>44615</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26648,7 +26654,7 @@
         <v>45098</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26721,7 +26727,7 @@
         <v>46202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26799,7 +26805,7 @@
         <v>46202</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26877,7 +26883,7 @@
         <v>46202</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26955,7 +26961,7 @@
         <v>46113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27033,7 +27039,7 @@
         <v>46113</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27111,7 +27117,7 @@
         <v>46119</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27189,7 +27195,7 @@
         <v>46200</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27262,7 +27268,7 @@
         <v>45754</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27335,7 +27341,7 @@
         <v>45834</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27413,7 +27419,7 @@
         <v>45708</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27486,7 +27492,7 @@
         <v>46202</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27564,7 +27570,7 @@
         <v>46126</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27642,7 +27648,7 @@
         <v>46202</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27720,7 +27726,7 @@
         <v>45208</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27798,7 +27804,7 @@
         <v>46202</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27876,7 +27882,7 @@
         <v>46129</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27954,7 +27960,7 @@
         <v>46128</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28027,7 +28033,7 @@
         <v>44914</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28100,7 +28106,7 @@
         <v>44944</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28173,7 +28179,7 @@
         <v>44867</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28251,7 +28257,7 @@
         <v>45362</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28324,7 +28330,7 @@
         <v>46203</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28397,7 +28403,7 @@
         <v>45462</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28470,7 +28476,7 @@
         <v>45511</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28543,7 +28549,7 @@
         <v>45596</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28616,7 +28622,7 @@
         <v>45009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28689,7 +28695,7 @@
         <v>45469</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28767,7 +28773,7 @@
         <v>46206</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28845,7 +28851,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28923,7 +28929,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29001,7 +29007,7 @@
         <v>45534</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29079,7 +29085,7 @@
         <v>46252</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29157,7 +29163,7 @@
         <v>46252</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29230,7 +29236,7 @@
         <v>46252</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29308,7 +29314,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29381,7 +29387,7 @@
         <v>46252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29454,7 +29460,7 @@
         <v>46252</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29532,7 +29538,7 @@
         <v>46252</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29610,7 +29616,7 @@
         <v>46252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29688,7 +29694,7 @@
         <v>45763</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29761,7 +29767,7 @@
         <v>45763</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29834,7 +29840,7 @@
         <v>45763</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29907,7 +29913,7 @@
         <v>46253</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29985,7 +29991,7 @@
         <v>45190</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30058,7 +30064,7 @@
         <v>46211</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30136,7 +30142,7 @@
         <v>46255</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30214,7 +30220,7 @@
         <v>46211</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30292,7 +30298,7 @@
         <v>46211</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30370,7 +30376,7 @@
         <v>45426</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30443,7 +30449,7 @@
         <v>46259</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30521,7 +30527,7 @@
         <v>46259</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30594,7 +30600,7 @@
         <v>46259</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30672,7 +30678,7 @@
         <v>46258</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30750,7 +30756,7 @@
         <v>45561</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30823,7 +30829,7 @@
         <v>46259</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30896,7 +30902,7 @@
         <v>45187</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30969,7 +30975,7 @@
         <v>44670</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31042,7 +31048,7 @@
         <v>45470</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31115,7 +31121,7 @@
         <v>46260</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31193,7 +31199,7 @@
         <v>44963</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31266,7 +31272,7 @@
         <v>45170</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31339,7 +31345,7 @@
         <v>44750</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31417,7 +31423,7 @@
         <v>45439</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31490,7 +31496,7 @@
         <v>45172</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31563,7 +31569,7 @@
         <v>45173</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31636,7 +31642,7 @@
         <v>45173</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31709,7 +31715,7 @@
         <v>46261</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31782,7 +31788,7 @@
         <v>46262</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31860,7 +31866,7 @@
         <v>45439</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31933,7 +31939,7 @@
         <v>45644</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32011,7 +32017,7 @@
         <v>46265</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32084,7 +32090,7 @@
         <v>45622</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32162,7 +32168,7 @@
         <v>46266</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32240,7 +32246,7 @@
         <v>46266</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32318,7 +32324,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32396,7 +32402,7 @@
         <v>45198</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32469,7 +32475,7 @@
         <v>45630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32547,7 +32553,7 @@
         <v>46268</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32620,7 +32626,7 @@
         <v>46268</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32693,7 +32699,7 @@
         <v>46268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32771,7 +32777,7 @@
         <v>46273</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32844,7 +32850,7 @@
         <v>45499</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32922,7 +32928,7 @@
         <v>46227</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33000,7 +33006,7 @@
         <v>44830</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33073,7 +33079,7 @@
         <v>44958</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33146,7 +33152,7 @@
         <v>46273</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33224,7 +33230,7 @@
         <v>46273</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33302,7 +33308,7 @@
         <v>46273</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33380,7 +33386,7 @@
         <v>46273</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33453,7 +33459,7 @@
         <v>46272</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33526,7 +33532,7 @@
         <v>46273</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33599,7 +33605,7 @@
         <v>46272</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33672,7 +33678,7 @@
         <v>46273</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33745,7 +33751,7 @@
         <v>45432</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33823,7 +33829,7 @@
         <v>46274</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33901,7 +33907,7 @@
         <v>46274</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33979,7 +33985,7 @@
         <v>46274</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34057,7 +34063,7 @@
         <v>46232</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34135,7 +34141,7 @@
         <v>46231</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34213,7 +34219,7 @@
         <v>46232</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34291,7 +34297,7 @@
         <v>46231</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34369,7 +34375,7 @@
         <v>46234</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34447,7 +34453,7 @@
         <v>45788</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34520,7 +34526,7 @@
         <v>45182</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34593,7 +34599,7 @@
         <v>45511</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34666,7 +34672,7 @@
         <v>45170</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34739,7 +34745,7 @@
         <v>45362</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34812,7 +34818,7 @@
         <v>46281</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34890,7 +34896,7 @@
         <v>45469</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34968,7 +34974,7 @@
         <v>45183</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35041,7 +35047,7 @@
         <v>46237</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35114,7 +35120,7 @@
         <v>45132</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35192,7 +35198,7 @@
         <v>46240</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35265,7 +35271,7 @@
         <v>46282</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35338,7 +35344,7 @@
         <v>45155</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35416,7 +35422,7 @@
         <v>44943</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35489,7 +35495,7 @@
         <v>45796</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35567,7 +35573,7 @@
         <v>46241</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35645,7 +35651,7 @@
         <v>46241</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35718,7 +35724,7 @@
         <v>46239</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35796,7 +35802,7 @@
         <v>45384</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35869,7 +35875,7 @@
         <v>45798</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35942,7 +35948,7 @@
         <v>45799</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36015,7 +36021,7 @@
         <v>46282</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36088,7 +36094,7 @@
         <v>45799</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36161,7 +36167,7 @@
         <v>45799</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36234,7 +36240,7 @@
         <v>46282</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36307,7 +36313,7 @@
         <v>45799</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36380,7 +36386,7 @@
         <v>46283</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36458,7 +36464,7 @@
         <v>45803</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36531,7 +36537,7 @@
         <v>46282</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36604,7 +36610,7 @@
         <v>46259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36682,7 +36688,7 @@
         <v>46282</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36755,7 +36761,7 @@
         <v>44482</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36828,7 +36834,7 @@
         <v>45537</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36906,7 +36912,7 @@
         <v>45441</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36979,7 +36985,7 @@
         <v>45462</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37052,7 +37058,7 @@
         <v>45523</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37125,7 +37131,7 @@
         <v>45426</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37198,7 +37204,7 @@
         <v>45821</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37276,7 +37282,7 @@
         <v>45824</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37354,7 +37360,7 @@
         <v>45824</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37432,7 +37438,7 @@
         <v>45341</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37510,7 +37516,7 @@
         <v>45833</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37583,7 +37589,7 @@
         <v>45833</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37656,7 +37662,7 @@
         <v>45838</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37734,7 +37740,7 @@
         <v>45840</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37812,7 +37818,7 @@
         <v>45840</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37890,7 +37896,7 @@
         <v>45840</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37963,7 +37969,7 @@
         <v>45842</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38041,7 +38047,7 @@
         <v>45842</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38114,7 +38120,7 @@
         <v>45617</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38187,7 +38193,7 @@
         <v>45842</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38265,7 +38271,7 @@
         <v>45849</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38343,7 +38349,7 @@
         <v>45855</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38421,7 +38427,7 @@
         <v>45858</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38494,7 +38500,7 @@
         <v>45433</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38572,7 +38578,7 @@
         <v>45202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38645,7 +38651,7 @@
         <v>45273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38718,7 +38724,7 @@
         <v>45439</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38796,7 +38802,7 @@
         <v>45860</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38874,7 +38880,7 @@
         <v>45620</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38947,7 +38953,7 @@
         <v>45859</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39025,7 +39031,7 @@
         <v>45271</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39103,7 +39109,7 @@
         <v>45450</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39176,7 +39182,7 @@
         <v>45870</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39254,7 +39260,7 @@
         <v>45870</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39332,7 +39338,7 @@
         <v>45877</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39405,7 +39411,7 @@
         <v>45882</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39483,7 +39489,7 @@
         <v>45881</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39561,7 +39567,7 @@
         <v>45000</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39634,7 +39640,7 @@
         <v>44635</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39707,7 +39713,7 @@
         <v>45250</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39785,7 +39791,7 @@
         <v>44559</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39863,7 +39869,7 @@
         <v>44635</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39936,7 +39942,7 @@
         <v>45029</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40009,7 +40015,7 @@
         <v>44635</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40082,7 +40088,7 @@
         <v>44742</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40155,7 +40161,7 @@
         <v>45553</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40228,7 +40234,7 @@
         <v>46070</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40306,7 +40312,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40379,7 +40385,7 @@
         <v>46111</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40452,7 +40458,7 @@
         <v>46111</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40525,7 +40531,7 @@
         <v>46119</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40598,7 +40604,7 @@
         <v>46147</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45482</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45897</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>46260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45531</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>46211</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46211</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>46227</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45832</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>46220</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45520</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45889</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46051</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45432</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45639</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>46133</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45462</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46190</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46272</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>46281</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45889</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>46135</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44466</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44742</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44838</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44820</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44872</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45618</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45719</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44893</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45208</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44876</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45428</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45132</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>46020</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45462</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45384</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45796</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45798</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>46029</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46031</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>46035</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>46035</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45439</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45974</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45891</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45894</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45085</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>45891</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45534</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45895</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>45898</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45901</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45551</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45551</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45551</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45901</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45799</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45799</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45611</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>45908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>45905</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>46055</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45209</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44944</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45912</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45178</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45009</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45923</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45924</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45923</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45925</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45037</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45930</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45930</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>46083</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45541</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45936</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>46090</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>46090</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>46093</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45943</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46105</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45947</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45950</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45623</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45426</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45622</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46106</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46106</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46107</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46107</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44657</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>46113</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>46113</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45462</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>46119</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45628</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45966</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45244</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45523</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45426</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45971</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45971</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45019</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45973</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45834</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45974</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46126</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45161</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46128</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>46129</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45981</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45981</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45644</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>46136</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45461</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45988</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45987</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45157</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45989</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45989</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45993</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45993</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45993</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45170</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45846</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45173</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45999</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45166</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45824</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45511</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45754</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45524</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>45310</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45877</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46008</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45821</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45341</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45824</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44468</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45257</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45727</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45174</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46142</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>46142</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>46143</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>46148</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45548</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>46153</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45833</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>46153</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45838</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>46155</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>46160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45941</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45840</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45842</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>46162</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45485</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>46162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45842</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45842</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45617</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45016</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45849</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45947</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45147</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45855</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45537</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44556</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45858</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45439</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45620</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45859</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45202</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45433</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45273</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45860</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>46171</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45098</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45157</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>46171</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45162</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44510</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45271</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45947</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45586</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45870</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45870</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46181</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>46181</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46183</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46183</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>46183</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>46183</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45450</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46182</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45114</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46183</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46183</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45602</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44963</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45274</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>46189</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45580</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45085</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45561</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>46196</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45877</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46197</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>46196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46196</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45172</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45068</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46200</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45882</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46203</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45881</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>46202</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45240</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45407</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45594</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45625</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45511</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>46252</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>46252</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>44594</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>46206</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>46252</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>46252</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46252</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46252</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46252</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46252</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46206</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45547</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45183</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>46211</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45665</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45708</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45754</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46258</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46255</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46259</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46259</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>46259</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45173</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45763</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45763</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45763</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45198</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>46259</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45208</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>46261</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45187</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45172</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>46262</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45173</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46266</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46265</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46268</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45163</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46268</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44608</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46272</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>46227</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45499</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45432</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>46272</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45306</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45450</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44945</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>46231</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>46274</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44867</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46273</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>46273</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>44848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45561</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>46274</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>46274</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46231</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46273</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>46232</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44872</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46232</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45167</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46237</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>46234</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>46239</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46282</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46282</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46282</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46259</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46282</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>46241</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46241</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>46240</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46283</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45478</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45965</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>46288</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>44893</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>46288</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45840</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>45540</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>46202</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>46290</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46290</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>46170</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45604</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>46290</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>46290</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44999</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45824</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44750</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45540</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44615</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45190</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45525</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44944</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45469</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45530</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>44914</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45511</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45511</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45168</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45161</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45156</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>44524</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45516</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>44963</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45609</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>45169</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>44867</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45462</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45462</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45750</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45107</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45439</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45168</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45160</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45362</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45163</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>45163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45644</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45175</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45470</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>44958</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44830</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45170</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45511</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45362</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45788</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45182</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45183</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45469</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>44635</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44559</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>44635</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>44635</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45000</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45250</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45029</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44742</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45553</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>46111</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>46070</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>46111</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>46119</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>46147</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45482</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45897</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>46260</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44545</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45531</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>46211</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46211</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>46227</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45981</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45544</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45832</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>46220</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45520</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45701</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45889</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46051</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45432</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45639</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>46133</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45462</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46190</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46272</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>46281</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45889</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>46135</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44466</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44742</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44838</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44820</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44872</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44487</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45618</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45719</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44893</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44867</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45208</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>44876</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45428</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45132</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>46020</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45462</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45384</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45796</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45798</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>46029</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46031</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>46035</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>46035</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45439</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45974</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45891</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45894</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45085</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45085</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>45891</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45534</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45895</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>45898</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45901</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45551</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45551</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45551</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>45901</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45799</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45799</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45611</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>45908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>45905</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>46055</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45209</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44944</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45912</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45178</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45009</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45922</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45923</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45924</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45923</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45925</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45037</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45930</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45930</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>46083</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45541</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45537</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45936</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>46090</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>46090</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>46093</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45943</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46105</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45947</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45950</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45623</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45426</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45622</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46106</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46106</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46107</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46107</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>44657</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>46113</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>46113</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45462</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>46119</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45628</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45966</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45244</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45523</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45426</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45971</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45971</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45019</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45973</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45834</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45974</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46126</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45161</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46128</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>46129</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45981</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45981</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45644</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>46136</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45461</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45988</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45184</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45987</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45157</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45989</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45989</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45993</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45993</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45993</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45170</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45846</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45173</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45999</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45166</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45824</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45511</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45754</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45524</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>45310</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45877</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46008</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45821</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45341</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45824</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44468</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45257</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45727</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45174</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46142</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>46142</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>46143</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>46148</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45548</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>46153</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45833</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>46153</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45838</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>46155</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>46160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45941</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45840</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45842</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>46162</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45485</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>46162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45842</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45842</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45617</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45016</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45849</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45947</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45147</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45855</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45537</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44556</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45858</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45439</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45620</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45859</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45202</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45433</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45273</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45860</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>46171</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45098</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45157</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>46171</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45162</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44510</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45271</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45947</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45586</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45870</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45870</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46181</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>46181</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>46183</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46183</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46183</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>46183</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>46183</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45450</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46182</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45114</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46183</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46183</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45602</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44963</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45274</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>46189</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45580</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45085</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45561</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>46196</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45877</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46197</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>46196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46196</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45172</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45068</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46200</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45882</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>46203</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45881</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>46202</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45240</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45407</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45594</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45625</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45511</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27363,7 +27363,7 @@
         <v>46252</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>46252</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>44594</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>46206</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>46252</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>46252</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46252</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46252</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46252</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46252</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46206</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45547</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45183</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>46211</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45665</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45708</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45754</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46258</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46255</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46259</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46259</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>46259</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45173</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45763</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45763</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45763</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45198</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>46259</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45208</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>46261</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45187</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45172</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>46262</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45173</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46266</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46265</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>46266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46268</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>45163</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46268</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44608</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46272</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>46227</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45499</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45432</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>46272</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45306</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45450</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44945</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>46231</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>46274</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44867</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46273</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>46273</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>46273</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>44848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45561</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>46274</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>46274</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46231</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46273</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>46232</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44872</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46232</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45167</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46237</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>46234</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>46239</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46282</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46282</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46282</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46259</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>46282</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>46241</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46241</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>46240</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46283</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45478</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45965</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>46288</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>44893</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>46288</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45840</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>45540</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>46202</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>46290</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46290</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>46170</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45604</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>46290</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>46290</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>44999</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45824</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44750</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>45540</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44615</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45190</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45525</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44944</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45469</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45530</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>44914</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45511</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45511</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45168</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45161</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45156</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>44524</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45516</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>44963</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45609</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>45169</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>44867</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45462</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45462</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45750</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>45107</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45439</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45168</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45160</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45362</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45163</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>45163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45644</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45175</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45470</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>44958</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44830</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45170</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45511</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45362</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45788</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45182</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45183</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45469</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>44635</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44559</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>44635</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>44635</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45000</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45250</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45029</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44742</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45553</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>46111</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>46070</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>46111</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>46119</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>46147</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45897</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>46260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46273</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45174</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45531</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46211</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>46211</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>46227</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45981</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44853</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>45520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>45832</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45544</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>46220</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46283</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>46051</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>46133</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>46190</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>46202</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45432</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>46272</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45639</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>46296</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>46135</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44742</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44615</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44838</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44476</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44820</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44872</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44487</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44872</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45173</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45511</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45170</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45068</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45016</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45362</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45240</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45085</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45580</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45469</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>46020</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45891</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45895</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45896</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45898</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>46031</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>46035</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>45901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>46035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>46035</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44893</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45905</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45908</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45891</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45209</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44999</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45155</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44943</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46042</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45796</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44594</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45384</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45912</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45183</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45912</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45166</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45916</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45798</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44482</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45922</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45923</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45161</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46055</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45925</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45930</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45930</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45537</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45936</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45604</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45936</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45943</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45947</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44893</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45441</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45950</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>46083</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45954</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45462</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46090</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>46090</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45960</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45523</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>46093</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45426</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45966</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45971</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45461</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45300</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45049</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45170</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45561</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45973</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45974</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45172</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>46106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>46105</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45511</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>46106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>46107</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45981</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45821</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45987</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45824</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45989</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45341</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45988</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46119</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45989</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45754</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45834</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46126</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45999</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>46129</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>46128</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45104</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45838</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45511</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45840</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45842</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45842</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45623</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45617</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45842</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45524</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>46136</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44848</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45665</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45855</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45824</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45182</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45858</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45433</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45310</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45202</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45273</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45511</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45439</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45902</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45860</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45846</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45620</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45859</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45540</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45244</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45877</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45271</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45541</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45168</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45628</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45611</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46143</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45450</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>46142</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45870</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46148</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45870</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45156</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46153</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>46155</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45485</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45167</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45169</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45175</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45545</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45941</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44657</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45609</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45877</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45604</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45530</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46162</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45157</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45727</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45947</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45160</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46171</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45882</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45157</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45881</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45407</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46171</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46176</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44867</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>46176</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45257</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45602</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46176</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>46177</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45161</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>44876</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45551</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45586</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>46181</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46183</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>46181</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45618</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45551</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46183</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44524</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44510</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46183</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>46183</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>44853</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46183</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>46183</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45548</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44963</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45037</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46189</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>46196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>46196</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45540</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>46196</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46196</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46197</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45551</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46202</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>46202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>46202</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>46200</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>46202</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>46202</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45163</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45750</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>46203</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45274</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>46211</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>46211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>46259</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44556</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>46259</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46259</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46259</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46260</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45533</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46261</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46262</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46265</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45525</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45547</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45085</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46266</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>46266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45161</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46266</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46268</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>46273</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45499</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>46227</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45178</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>46273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>46272</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>46273</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>46272</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>46273</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45432</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>45019</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>46274</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>46274</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>46274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>46232</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>46231</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>46232</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>46231</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46234</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>45450</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45462</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45462</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>46281</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45719</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>46237</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>46240</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45163</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>46282</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45306</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>46282</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46282</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>46283</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>46282</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>46259</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>46282</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45478</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46241</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45428</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45044</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44615</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45098</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>46241</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46288</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>46288</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45754</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45708</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45840</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46290</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45208</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46293</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46202</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45824</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44914</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>46293</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>46293</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>46293</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46290</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>46290</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>44944</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>46170</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45362</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46252</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46252</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>46252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45462</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45596</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46252</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45469</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>46252</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>46252</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>46252</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>44869</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>46296</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>46297</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45926</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>46253</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46296</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>46185</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46255</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45923</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45534</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45763</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45763</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45763</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45190</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45426</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45561</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45187</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44670</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45470</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>44963</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45170</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>44750</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45439</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45172</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45173</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>45173</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45439</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45644</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45622</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45198</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>44830</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>44958</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45788</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>45182</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45000</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>44635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45250</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>44559</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>44635</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45029</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44635</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44742</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45553</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>46070</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>46111</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46111</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>46111</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>46119</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>46147</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45897</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>46260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>46214</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46273</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45174</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45531</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46211</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>46211</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>46227</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45981</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45981</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44853</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>45520</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>45832</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45544</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>46220</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46283</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45701</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>46051</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45946</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>46133</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>46190</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>46202</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45432</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>46272</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45639</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>46296</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>46135</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44742</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44615</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44838</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>44476</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44820</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44872</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44487</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>44872</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45173</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45511</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45170</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45068</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45016</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45362</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45240</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45085</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45580</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45469</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>46020</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45891</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45895</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45896</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45898</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>46031</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>46035</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>45901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>46035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>46035</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44893</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45974</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45905</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45908</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45891</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45209</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44999</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45155</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44943</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46042</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45796</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44594</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45384</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45912</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45183</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45912</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45166</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45916</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45798</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45799</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45799</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44482</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45922</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45923</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45161</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46055</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45925</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45147</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45930</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45930</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45537</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45936</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45604</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45936</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45943</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45947</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44893</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45441</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45950</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>46083</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45954</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45462</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46090</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>46090</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45960</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45523</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>46093</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45426</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45966</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45971</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45461</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45300</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45049</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45170</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45561</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45973</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45974</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45172</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>46106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>46105</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45511</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>46106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>46107</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45981</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45821</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45987</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45824</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45989</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45341</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45988</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46119</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45989</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45754</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45834</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46126</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45999</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>46129</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>46128</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45104</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45838</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45511</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45840</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45842</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45842</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45623</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45617</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45842</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45524</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>46136</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44848</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45665</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45855</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45824</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45182</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45858</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45433</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45310</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45202</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45273</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45511</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45439</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45902</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45860</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45846</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45620</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45859</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45540</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45244</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45877</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45271</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45541</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45168</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45628</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45611</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46143</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45450</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>46142</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45870</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46148</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45870</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45156</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46153</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>46155</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45485</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45167</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45169</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45175</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>45545</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45941</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44657</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45609</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45877</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45604</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45530</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46162</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45157</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45727</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45947</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45160</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46171</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45882</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45157</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45881</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45407</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46171</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46176</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44867</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>46176</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45257</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45602</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46176</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>46177</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45161</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>44876</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45551</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45586</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>46181</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46183</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>46181</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45618</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45551</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46183</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44524</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44510</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46183</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>46183</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>44853</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46183</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>46183</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45548</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44963</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45037</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46189</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>46196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>46196</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45540</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>46196</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46196</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46197</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45551</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>46202</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>46202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>46202</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>46200</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>46202</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>46202</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45163</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45750</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>46203</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45274</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>46211</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>46211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>46259</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44556</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>46259</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46259</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46259</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46260</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45533</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46261</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46262</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46265</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45525</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45547</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45085</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46266</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>46266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45161</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46266</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46268</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>46273</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45499</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>46227</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45178</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>46273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>46272</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>46273</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>46272</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>46273</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45432</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>45019</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>46274</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>46274</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>46274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>46232</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>46231</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>46232</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>46231</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46234</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>45450</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45462</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45462</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>46281</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45719</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>46237</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>46240</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45163</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>46282</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45306</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>46282</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46282</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>46283</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>46282</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>46259</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>46282</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45478</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46241</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45428</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45044</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44615</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45098</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>46241</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46288</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>46288</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45754</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45708</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45840</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46290</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45208</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46293</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46202</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45824</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44914</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>46293</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>46293</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>46293</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46290</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>46290</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>44944</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>46170</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44867</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45362</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46252</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46252</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>46252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45462</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45596</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46252</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45469</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>46252</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>46252</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>46252</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>44869</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>46296</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>46297</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>45926</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>46253</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46296</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>46185</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46255</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45923</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45534</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45763</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45763</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45763</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45190</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45426</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45561</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45187</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44670</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45470</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>44963</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45170</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>44750</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45439</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45172</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>45173</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>45173</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45439</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45644</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45622</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45198</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>44830</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>44958</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45788</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>45182</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45000</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>44635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45250</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>44559</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>44635</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45029</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>44635</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44742</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45553</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>46070</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>46111</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46111</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>46111</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>46119</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>46147</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45482</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45897</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>45853</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46288</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>46260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45174</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>46214</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>46281</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46227</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>44853</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45832</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45544</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45981</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45520</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>46220</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>46281</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46283</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45462</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45432</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45946</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>46133</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>46190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>46202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>46272</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>46296</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45639</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>46135</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44602</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>44820</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44487</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44838</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44872</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44867</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>45533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44869</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45049</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44818</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45548</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44876</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45618</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45156</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44524</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45428</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44963</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45609</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45169</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44853</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45517</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44867</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45462</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45462</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44893</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45208</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45016</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45147</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45240</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45750</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45537</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>44556</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45300</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45439</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45168</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>45462</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45160</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45362</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>45163</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45163</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>45163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>45890</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45596</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45162</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44510</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45891</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45896</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45896</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45895</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45644</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45439</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45085</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45085</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45908</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45470</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45908</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45905</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45551</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45551</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44958</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44830</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45912</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45916</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45114</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45611</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45044</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45602</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45209</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45511</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44963</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45922</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45274</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45009</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45580</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45362</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45788</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45085</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45923</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45924</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45561</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45925</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45037</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45930</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45132</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>44943</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45384</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45172</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45184</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45068</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45796</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45541</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45604</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45799</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45799</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45799</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45407</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45936</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45625</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45803</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45511</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>44482</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44594</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>45537</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45623</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45426</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45622</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>45547</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45183</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45462</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45665</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45441</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45523</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45426</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44657</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45708</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45821</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45947</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45341</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45628</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45947</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45824</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44670</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45173</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45019</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45763</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45763</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45763</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>45198</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45208</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45833</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45833</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45187</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45838</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45170</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45161</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45172</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45840</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45842</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45842</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45461</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45971</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45617</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45173</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45184</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45157</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45973</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45855</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45170</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45858</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45439</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45620</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45173</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45859</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45433</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45273</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45860</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45166</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45271</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44608</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45870</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45306</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45870</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45754</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45450</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45450</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>44945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44867</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44848</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45561</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45877</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45981</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44872</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45882</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45881</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45167</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45257</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45727</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45174</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46106</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46107</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>45988</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46107</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45987</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45989</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>46113</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45989</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>46113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45993</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>46128</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44893</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45540</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>46136</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45604</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>44999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>46020</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44750</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45540</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45846</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45824</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45511</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45511</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>46031</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44615</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45524</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>46035</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45310</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45877</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>46035</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45190</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45104</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>46035</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>46035</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45891</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>46042</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45525</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45902</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44944</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45469</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>45530</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45511</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45168</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>46055</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>46062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>46142</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>46142</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>46143</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>46153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>46083</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46090</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>46160</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>46090</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45545</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45941</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>46093</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>46162</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45485</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>46162</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45947</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46171</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>46171</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>46176</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45947</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45586</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>46176</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46177</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>46176</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46183</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>46183</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>46183</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>46183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46182</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>46189</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>46196</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46197</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46196</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>46196</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>46196</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46200</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>46202</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>46202</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46203</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46202</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>46202</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>46206</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46206</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>46206</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>46211</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>46211</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>46211</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46265</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>46266</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>46266</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>46268</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>46268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>46268</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>46272</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>46227</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45499</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45432</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>46272</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46231</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>46274</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>46273</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46273</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>46231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>46273</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>46232</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>46232</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46237</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>46234</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46239</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>46282</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46282</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>46282</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>46282</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46282</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>46241</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>46241</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>46240</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46283</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45478</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45965</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46288</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45840</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>46202</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46290</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46290</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46170</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>46290</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>46290</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45824</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46293</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>46293</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46293</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46293</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>46252</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>46252</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46253</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>46296</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>46252</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>46252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>46252</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>46296</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45842</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46181</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>46252</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>45923</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>46297</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>44869</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45926</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>46185</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46297</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46258</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46259</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46259</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>46259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>46259</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>46261</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>46262</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>46304</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46259</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>46260</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44635</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44559</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>44635</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45000</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45250</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45029</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>44742</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45553</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>46111</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>46070</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46111</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46111</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46119</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46147</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45482</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45897</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>45853</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46288</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>46260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45174</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>46214</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>46281</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46227</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>44853</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45981</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45832</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45544</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45981</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45520</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>46220</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>46281</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46283</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45462</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45432</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45946</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>46133</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>46190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>46202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>46272</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>46296</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45639</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>46135</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44602</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>44820</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>44879</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44487</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44838</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44872</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44867</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>45533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44869</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45049</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44818</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45548</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44876</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45618</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45156</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44524</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45428</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44963</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45609</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45169</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44853</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45517</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44867</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45462</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45462</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44893</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45208</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45016</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45147</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45240</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45750</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45537</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>44556</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45300</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>45439</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45168</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>45462</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45160</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45362</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>45163</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45163</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>45163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>45890</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45596</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45162</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44510</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45891</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45896</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45896</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45895</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45644</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45439</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45085</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45085</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45908</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45470</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45908</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45905</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45551</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45551</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44958</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44830</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45912</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45916</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45114</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45611</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45044</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45602</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45209</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44944</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45511</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44963</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45922</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45274</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45009</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45580</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45362</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45788</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45085</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45923</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45924</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45561</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45925</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45037</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45930</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45132</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>44943</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45384</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45172</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45184</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45068</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45796</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45541</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45604</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45799</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45799</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45799</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45407</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45936</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45625</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45803</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45511</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>44482</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44594</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>45537</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45623</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45426</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45622</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>45547</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45183</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45462</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45665</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45441</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45523</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45426</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44657</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45708</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45821</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45947</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45341</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45628</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45947</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45824</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44670</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45173</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45019</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45763</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45763</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45763</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>45198</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45208</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45833</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45833</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45187</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45838</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45170</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45182</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45161</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45172</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45840</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45842</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45842</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45461</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45971</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45617</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45173</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45184</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45157</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45973</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45855</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45170</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45858</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45439</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45620</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45173</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45859</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45433</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45273</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45860</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45166</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45271</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44608</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45870</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45306</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45870</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45754</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45450</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45450</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>44945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44867</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44848</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45561</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45877</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45981</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44872</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45882</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45881</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45167</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45257</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45727</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45174</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>46106</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46107</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>45988</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46107</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45987</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45989</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>46113</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45989</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>46113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45993</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45993</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>46128</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44893</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45540</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>46136</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45604</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>44999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>46020</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44750</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45540</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45846</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>45824</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45511</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45511</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>46031</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44615</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45524</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>46035</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45310</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45877</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>46035</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45190</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45104</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>46035</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>46035</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45891</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>46042</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45525</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45902</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44944</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45469</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>45530</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45511</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45168</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>46055</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>46062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>46142</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>46142</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>46143</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>46153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>46083</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46090</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>46160</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>46090</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45545</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45941</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>46093</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>46162</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45485</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>46162</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45947</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>46171</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>46171</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>46176</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45947</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45586</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>46176</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46177</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>46176</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46183</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>46183</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>46183</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>46183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46182</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>46189</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>46196</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46197</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46196</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>46196</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>46196</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46200</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>46202</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>46202</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>46203</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46202</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>46202</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>46206</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46206</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>46206</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>46211</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>46211</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>46211</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>46266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46265</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>46266</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>46266</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>46268</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>46268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>46268</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>46272</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>46227</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45499</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45432</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>46272</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46231</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>46274</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>46273</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46273</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>46231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>46273</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>46232</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>46232</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46237</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>46234</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46239</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>46282</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>46282</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>46282</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>46282</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46282</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>46241</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>46241</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>46240</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46283</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45478</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45965</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46288</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45840</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>46202</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46290</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46290</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46170</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>46290</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>46290</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45824</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46293</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>46293</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46293</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46293</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>46252</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>46252</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46253</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>46296</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>46252</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>46252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>46252</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>46296</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45842</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46181</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>46252</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>45923</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>46297</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>44869</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45926</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>46185</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46297</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46258</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46259</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46259</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>46259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>46259</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>46261</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>46262</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>46304</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46259</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>46260</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44635</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44559</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>44635</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45000</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45250</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45029</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>44742</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45553</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>46111</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>46070</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46111</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46111</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46119</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46147</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45897</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>46288</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>46260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46214</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>46273</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46281</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>46227</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44853</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>45520</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45544</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>46220</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>46283</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45832</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45462</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45946</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>46190</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45432</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>46202</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>46133</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>46272</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45639</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>46296</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>46309</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>46135</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44602</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44820</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44872</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44879</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44869</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45537</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45173</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45068</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45016</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>45085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>45085</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45644</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>45580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44893</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45209</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45166</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45147</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45517</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45604</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45208</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44893</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45174</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45461</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45049</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45170</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45561</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45172</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45524</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45594</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45240</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45754</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45824</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45890</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>45891</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45895</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45894</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45896</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45896</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45310</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45902</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45846</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>45877</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45104</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45905</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>46143</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46142</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45912</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>46142</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45623</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45922</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45923</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45924</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45925</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46148</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45665</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45930</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>46153</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46153</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45936</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45168</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45936</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45943</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45947</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45950</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45244</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45954</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46155</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45485</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45960</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45541</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45168</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45628</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45545</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45611</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45966</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45941</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45971</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>46160</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>46162</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45973</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45973</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45974</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45156</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45981</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45987</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45947</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45989</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45988</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45989</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45167</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45169</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44945</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45993</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45993</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45993</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44657</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45604</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45530</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45999</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45157</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46171</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45160</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44944</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45157</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45407</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44867</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46020</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44876</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45551</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46171</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45618</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45551</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>46176</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>44524</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44510</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44853</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46176</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46035</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45548</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>46035</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>46176</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46035</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46035</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45947</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45891</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44963</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45037</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45586</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>46183</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>46182</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46183</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46183</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45184</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>46183</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45551</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46183</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>46062</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46183</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45163</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45750</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>46083</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45274</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45511</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>46090</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>46090</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46189</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46093</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44556</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45533</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46196</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>46106</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46196</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46196</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>46107</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>46197</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45525</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45547</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46113</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>46113</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45085</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>46202</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46119</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46202</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46200</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46126</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>46202</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>46129</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>46128</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45019</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>46203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45450</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45462</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45462</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46206</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45719</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45511</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>46206</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45114</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45306</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>46211</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>46211</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45428</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44615</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46273</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45499</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46227</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45754</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>46273</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>46272</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>46273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45708</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>46272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46273</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45432</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45208</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46232</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44914</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46231</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>46232</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>46231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>44944</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>46234</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44867</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45362</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45462</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45596</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45009</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45469</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46237</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46239</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46282</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46283</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>46282</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>46282</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45965</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45478</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>46241</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45534</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45763</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45763</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45763</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46241</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46288</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45426</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45840</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46290</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45561</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45187</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>44670</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46293</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>46202</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45824</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>46293</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45470</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44963</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46293</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46290</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46290</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44750</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46290</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46170</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45439</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45172</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45173</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45173</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>46252</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>46252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>46252</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45439</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45644</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>46252</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46252</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>46252</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45622</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>44869</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>46296</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46297</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45926</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>46253</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>46252</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46296</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46185</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45923</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46297</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45198</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45842</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44830</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>44958</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>46258</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46255</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45788</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45511</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45170</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46259</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45362</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46259</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46260</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45469</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45183</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>46259</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46307</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46259</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45132</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45155</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44943</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45796</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46307</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45384</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46261</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45798</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45799</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45799</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>46304</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45799</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>46262</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45799</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>46307</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46307</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45803</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46309</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>46265</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>46309</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>46309</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46309</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46309</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46309</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46309</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46309</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>46309</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>46266</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>46266</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46266</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>46308</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45537</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>46309</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>46308</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45441</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46310</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45462</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45523</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45426</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>45821</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46268</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45824</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45341</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>46268</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45833</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45833</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45838</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45840</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45842</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45842</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45617</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45855</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45858</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45433</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45273</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45439</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45860</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>45620</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45859</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45271</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45450</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45870</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45870</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45877</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45882</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45881</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>44635</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45250</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>44559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44635</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45029</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>44635</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44742</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45553</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>46070</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46111</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>46119</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>46147</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45482</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45897</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>46288</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>46260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46214</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>46273</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46281</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>46227</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44853</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>45520</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45544</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>46220</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>46283</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45832</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45701</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45462</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45946</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>46190</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45432</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>46202</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>46133</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>46272</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45639</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>46296</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>46309</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>46135</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44602</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44820</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44872</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44879</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44487</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44869</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44818</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44872</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45537</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45173</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45068</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45016</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45219</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>45085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>45085</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45644</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>45580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44893</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45209</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45166</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45183</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45147</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45517</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45604</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45208</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44893</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45174</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45461</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45049</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45170</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45561</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45172</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45524</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45594</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45240</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45754</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45824</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45890</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>45891</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45895</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45894</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45896</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45896</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45310</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45902</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45846</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>45877</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45104</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45905</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>46143</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46142</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45912</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>46142</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45623</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45922</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45923</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45924</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45925</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46148</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45665</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45930</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>46153</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46153</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45936</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45168</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45936</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45943</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45947</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45950</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45244</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45954</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46155</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45485</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45960</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45541</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45168</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45628</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45545</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45611</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45966</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45941</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45971</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>46160</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>46162</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45973</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45973</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45974</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45156</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45981</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45987</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45947</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45989</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45988</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45989</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45167</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45169</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44945</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45993</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45993</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45993</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44657</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45604</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45530</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45999</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45157</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46171</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45160</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44944</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45157</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45407</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44867</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46020</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44876</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45551</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46171</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45618</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45551</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>46176</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>44524</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44510</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44853</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46176</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46035</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45548</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>46035</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>46176</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46035</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46035</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45947</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45891</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44963</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45037</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45586</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>46183</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>46182</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46183</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46183</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45184</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>46183</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45551</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46183</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>46062</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46183</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45163</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45750</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>46083</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45274</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45511</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>46090</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>46090</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46189</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46093</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44556</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45533</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46196</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>46106</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46196</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46196</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>46107</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>46197</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45525</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45547</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46113</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>46113</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45085</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>46202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>46202</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46119</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46202</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46200</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46126</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>46202</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>46129</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>46128</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>46202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45019</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>46203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45450</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45462</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45462</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46206</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45719</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45511</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45163</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>46206</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45114</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45306</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>46211</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>46211</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45428</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44615</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46273</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45499</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46227</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45754</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>46273</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>46272</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>46273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45708</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>46272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46273</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45432</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45208</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>46232</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44914</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46231</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>46232</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>46231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>44944</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>46234</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44867</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45362</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45462</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45596</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45009</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45469</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46237</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46240</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46239</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>46282</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46283</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>46282</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>46282</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45965</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>45478</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>46241</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45534</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45763</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45763</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45763</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46241</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46288</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45426</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45840</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46290</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45561</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45187</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>44670</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46293</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>46202</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45824</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>46293</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45470</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44963</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46293</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46290</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46290</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44750</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46290</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46170</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45439</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45172</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45173</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45173</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>46252</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>46252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>46252</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45439</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45644</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>46252</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46252</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>46252</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45622</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>44869</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>46296</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46297</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45926</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>46253</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>46252</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46296</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46185</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45923</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46297</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45198</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45842</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44830</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>44958</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>46258</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46255</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45788</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45511</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45170</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46259</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45362</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46259</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46260</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45469</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45183</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>46259</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46307</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46259</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45132</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45155</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44943</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45796</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46307</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45384</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46261</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45798</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45799</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45799</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>46304</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45799</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>46262</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45799</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>46307</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46307</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45803</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46309</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>46265</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>46309</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>46309</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46309</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46309</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46309</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46309</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46309</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>46309</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>46266</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>46266</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46266</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>46308</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45537</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>46309</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>46308</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45441</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46310</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45462</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45523</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45426</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>45821</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46268</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>45824</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45341</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>46268</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45833</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45833</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45838</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45840</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45842</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45842</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45617</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45855</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45858</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45433</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45273</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45439</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45860</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>45620</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45859</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45271</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45450</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45870</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45870</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45877</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45882</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45881</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>44635</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>45250</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>44559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44635</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45029</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>44635</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44742</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45553</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>46070</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46111</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>46111</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>46119</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>46147</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45482</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>46288</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>45897</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46260</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46214</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>46281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>46227</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45520</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>46220</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46283</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46314</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45544</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45701</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46190</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>45946</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>46202</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46010</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>46296</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45639</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>46133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>46309</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45432</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45462</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>46135</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44830</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44546</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44742</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44838</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44872</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44879</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44869</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45618</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45540</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45604</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44893</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45208</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45901</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45901</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45533</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45540</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45908</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45908</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>45905</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45941</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45485</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>46162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45912</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45916</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45190</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45104</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45947</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45924</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45930</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44876</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>46171</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>46171</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44944</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45469</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45530</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>44914</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45511</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45943</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>46176</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45586</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>46176</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>46176</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44853</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45161</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45156</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44524</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45947</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45947</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46183</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46183</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>46183</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46183</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46182</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45954</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45609</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>46183</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45163</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>46183</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45960</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>44867</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>46189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45462</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45462</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46196</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45971</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45750</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45973</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45107</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45300</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45439</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45168</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46200</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>46202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46202</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45160</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46203</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45981</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45981</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>46202</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45362</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45163</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45163</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45988</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>46206</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>46206</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45644</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45987</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46206</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46211</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45989</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>46211</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45989</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45175</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45993</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45993</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45993</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45470</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>44958</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44830</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46227</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45499</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45432</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46231</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>46232</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>46232</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45511</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46237</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46234</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46239</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>46020</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45462</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45362</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45788</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>46282</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46282</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45183</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>46241</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45469</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>46031</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>46241</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46035</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>46035</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46240</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>46035</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>46283</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45132</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44943</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45478</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45163</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45891</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45384</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45155</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>46042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45796</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45798</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>46288</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45799</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45799</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45799</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45840</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>46202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>46290</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45803</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46290</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>46170</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>46290</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>46290</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45537</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>46062</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>46293</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45462</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45441</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45523</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45426</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46293</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46293</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46293</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45821</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45341</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45824</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>46252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46252</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>46296</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>46083</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>46252</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>46252</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46252</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46296</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45842</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46181</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45833</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>46252</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45833</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45596</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>46090</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45838</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45923</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46297</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45840</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46255</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45842</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45842</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>44869</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45926</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>46185</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45617</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46297</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>46105</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>46258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>46259</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>46106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>46259</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>46107</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>46107</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>46259</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45855</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45858</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>45439</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45620</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45859</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45433</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45273</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45860</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>46113</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>46113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45271</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>46261</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46119</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45439</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45870</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45870</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45450</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46304</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46259</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>46260</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45834</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46126</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45085</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45085</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45877</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>46308</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45534</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>46307</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>46128</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>46129</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45881</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45551</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45551</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45551</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45240</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46307</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46262</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>46307</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45611</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>46136</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>46307</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>46265</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>46309</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>46266</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>46309</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>46309</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>46309</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46309</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46308</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45209</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44944</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46309</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>46309</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46309</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45178</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46266</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>46309</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46310</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45846</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>46268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45824</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45511</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46268</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45511</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45524</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45310</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46268</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>46314</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45877</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46272</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46273</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46272</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45037</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46273</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46273</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45902</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46315</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>46314</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>46316</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46273</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46317</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45541</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>46318</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45604</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46317</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>46142</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>46142</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>46274</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>46143</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>46148</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46153</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45623</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>45426</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>46153</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45622</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46155</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44657</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>46160</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45545</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45628</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45244</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45019</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45161</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45644</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45461</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45184</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45157</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45170</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45173</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45166</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45754</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45161</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45257</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45727</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45174</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45049</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45548</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45517</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45016</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45147</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45537</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>44556</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45098</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45157</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45162</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>44510</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45114</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>45044</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45602</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>44963</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45274</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45580</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45085</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45561</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45172</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>45184</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45068</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45407</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45594</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45625</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45511</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44594</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45547</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45665</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>45708</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>45754</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>44670</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45173</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>45763</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45763</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45763</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45198</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45208</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45187</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45170</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45182</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45172</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45173</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45163</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44608</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45306</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45450</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>44945</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>44867</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>44848</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45561</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>44872</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>45167</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44893</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44635</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44559</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44635</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44635</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45000</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45250</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45029</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>44742</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45553</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46111</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46070</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46111</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46111</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46119</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>46147</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>

--- a/Översikt NORSJÖ.xlsx
+++ b/Översikt NORSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45840</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>46198</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>46202</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>46202</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46253</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>45482</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>46288</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>45897</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>46260</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46214</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>46281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44545</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>45531</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>46227</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45981</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45520</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>46220</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46283</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46314</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45544</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45701</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>46190</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>45946</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>46202</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46010</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>46296</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45639</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>46133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>46309</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45432</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45462</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>46135</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44830</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44546</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44742</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44838</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44872</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44879</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44869</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44818</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45618</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45540</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45604</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44893</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45208</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45901</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45901</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45533</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45540</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45908</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45908</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>45905</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45941</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45485</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>46162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45912</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45916</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44615</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45190</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45104</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45947</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45924</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45930</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44876</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>46171</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>46171</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44944</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>45469</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45530</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>44914</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45511</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45943</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45428</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>46176</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45586</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>46176</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>46176</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44853</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45161</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45156</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>44524</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45947</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45947</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46183</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46183</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>46183</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46183</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46182</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45954</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45609</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>46183</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45163</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>46183</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45960</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>44867</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>46189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45462</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45462</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46196</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45971</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45750</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45973</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>46196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46196</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45107</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45300</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45439</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45168</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46200</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>46202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46202</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45160</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46203</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45981</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45981</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>46202</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45362</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45163</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45163</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45988</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>46206</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>46206</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45644</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45987</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46206</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46211</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45989</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>46211</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45989</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45175</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45993</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45993</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45993</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45470</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>44958</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44830</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46227</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45499</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45432</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46231</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>46232</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>46232</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45511</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46237</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46234</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46239</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>46282</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>46020</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45462</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45362</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45788</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>46282</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46282</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45183</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>46241</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45469</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>46031</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>46241</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46035</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>46035</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46240</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>46035</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>46283</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45132</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44943</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45478</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45163</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45891</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45384</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45155</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>46042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45796</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45798</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>46288</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45799</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45799</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45799</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45840</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>46202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>46290</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45803</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46290</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>46170</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>46290</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>46290</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45537</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>46062</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>46293</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45462</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45441</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45523</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45426</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46293</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46293</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46293</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45821</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45341</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45824</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>46252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46252</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>46296</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>46083</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>46252</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>46252</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46252</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46296</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45842</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46181</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45833</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>46252</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45833</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45596</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>46090</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45838</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45923</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46297</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45840</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46255</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45842</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45842</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>44869</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45926</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>46185</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45617</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46297</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>46105</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>46258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>46259</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>46106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>46259</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>46107</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>46107</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>46259</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45855</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45858</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>45439</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45620</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45859</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45433</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45273</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45860</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>46113</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>46113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45271</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>46261</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46119</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45439</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45870</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45870</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45450</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46304</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46259</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>46260</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45834</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46126</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45085</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45085</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45877</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>46308</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45534</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>46307</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>46128</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>46129</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45881</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45551</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45551</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45551</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45240</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>46307</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46262</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>46307</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45611</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>46136</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>46307</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>46265</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>46309</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>46266</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>46309</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>46309</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>46309</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46309</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46308</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45209</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44944</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46309</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>46309</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46309</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45178</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46266</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>46309</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46310</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45846</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>46268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45824</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45511</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46268</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45511</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45524</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45310</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46268</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>46314</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45877</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46272</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46273</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46272</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45037</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46273</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46273</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45902</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46315</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>46314</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>46316</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46273</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46317</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45541</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>46318</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45604</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46317</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>46142</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>46142</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>46274</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>46143</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>46148</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46153</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45623</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>45426</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>46153</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45622</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46155</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44657</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>46160</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45545</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45628</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45244</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45019</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45161</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45644</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45461</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45184</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45157</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45170</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45173</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45166</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>45754</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45161</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45257</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45727</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45174</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45049</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45548</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45517</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45016</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45147</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45537</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>44556</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45098</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45157</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45162</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>44510</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45114</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>45044</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45602</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>44963</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45274</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45580</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45085</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45561</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45172</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>45184</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45068</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45407</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45594</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45625</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45511</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44594</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45547</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45665</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>45708</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>45754</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>44670</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45173</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>45763</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45763</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45763</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45198</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45208</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45187</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45170</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45182</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45172</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45173</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45163</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44608</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45306</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45450</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>44945</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>44867</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>44848</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45561</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>44872</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>45167</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44893</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>44635</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44559</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44635</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44635</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45000</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45250</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45029</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>44742</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45553</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46111</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46070</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46111</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46111</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46119</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>46147</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
